--- a/examples/Template-Workplan.xlsx
+++ b/examples/Template-Workplan.xlsx
@@ -1,14 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ohageby/work/objectStore/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BF977FC-9CB2-D245-816D-427007D6DD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{2BF977FC-9CB2-D245-816D-427007D6DD51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31B80B53-C69F-B943-A604-361A7DCEF6C8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="32660" windowHeight="18500" xr2:uid="{3E8C7C52-3CFF-4937-8C79-1C9B8DF9D164}"/>
   </bookViews>
@@ -86,7 +81,7 @@
     <t>L</t>
   </si>
   <si>
-    <t>Pankaj</t>
+    <t>Alice</t>
   </si>
   <si>
     <t>Yes</t>
@@ -197,10 +192,10 @@
     <t>open</t>
   </si>
   <si>
-    <t>Dan</t>
-  </si>
-  <si>
-    <t>Sue</t>
+    <t>Ben</t>
+  </si>
+  <si>
+    <t>Chen</t>
   </si>
 </sst>
 </file>
@@ -682,7 +677,7 @@
     </row>
     <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="9">
-        <f t="shared" ref="A2:A73" si="0">ROW()-1</f>
+        <f t="shared" ref="A2:A19" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1071,7 +1066,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1721,7 +1716,7 @@
     </row>
     <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="9">
-        <f t="shared" ref="A66:A80" si="1">ROW()-1</f>
+        <f t="shared" ref="A72:A80" si="1">ROW()-1</f>
         <v>71</v>
       </c>
       <c r="B72" s="8" t="s">
